--- a/public/templates/water-template.xlsx
+++ b/public/templates/water-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthika Suresh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hackathon\ESGroww\ESGroww\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{281F46BD-5F4A-4960-AD7A-0502ECF3B903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175F4E23-D429-4CEC-9DBA-E7BB22C86410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{81D6577E-5736-4984-B94B-4417C42068DE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{81D6577E-5736-4984-B94B-4417C42068DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,25 +34,70 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>waterKl</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>recycledWaterKl</t>
+  </si>
+  <si>
+    <t>💧  Water Consumption Upload Template</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>Municipal_Water</t>
+  </si>
+  <si>
+    <t>Tanker_Water</t>
+  </si>
+  <si>
+    <t>Borewell_Water</t>
+  </si>
+  <si>
+    <t>Rainwater_Harvested</t>
+  </si>
+  <si>
+    <t>Total_Water_Consumption</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Month of data entry. Enter as number (1–12) or text (Jan–Dec / January–December).</t>
+  </si>
+  <si>
+    <t>4-digit calendar year of the data entry.</t>
+  </si>
+  <si>
+    <t>Volume of water received from municipal / BWSSB / civic body supply during the month.</t>
+  </si>
+  <si>
+    <t>Volume of water purchased via private water tankers during the month. Enter 0 if none.</t>
+  </si>
+  <si>
+    <t>Volume of groundwater extracted from borewell / open well during the month. Enter 0 if none.</t>
+  </si>
+  <si>
+    <t>Volume of rainwater collected and used from rainwater harvesting systems. Enter 0 if none.</t>
+  </si>
+  <si>
+    <t>Volume of treated wastewater (STP/ETP output) reused within the facility during the month.</t>
+  </si>
+  <si>
+    <t>Sum of all water sources for the month. Must equal Municipal + Tanker + Borewell + Rainwater + Recycled.</t>
+  </si>
+  <si>
+    <t>Total water procurement cost for the month — municipal bill + tanker invoices. In INR.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,22 +107,50 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF1A5276"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A5276"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF117A65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -85,14 +158,78 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -408,24 +545,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B63C61E1-6ABC-492F-87AD-07ED05BF0AE2}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>